--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V3.3 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="V3.4 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.3 核对清单'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.4 核对清单'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -3706,136 +3706,120 @@
     </row>
     <row r="113" ht="19" customHeight="1"/>
     <row r="114" ht="19" customHeight="1">
-      <c r="A114" s="14" t="inlineStr"/>
-      <c r="B114" s="15" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E114" s="14" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>125.1, 105.2</t>
         </is>
       </c>
-      <c r="F114" s="16" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>3 脚不对称，贴不反</t>
-        </is>
-      </c>
+      <c r="G114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="19" customHeight="1">
-      <c r="A115" s="14" t="inlineStr"/>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr"/>
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C115" s="16" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D115" s="16" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E115" s="14" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>132.0, 62.1</t>
         </is>
       </c>
-      <c r="F115" s="16" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G115" s="17" t="inlineStr">
-        <is>
-          <t>3 脚不对称，贴不反</t>
-        </is>
-      </c>
+      <c r="G115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="19" customHeight="1">
-      <c r="A116" s="14" t="inlineStr"/>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr"/>
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E116" s="14" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>84.0, 62.1</t>
         </is>
       </c>
-      <c r="F116" s="16" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>3 脚不对称，贴不反</t>
-        </is>
-      </c>
+      <c r="G116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="19" customHeight="1">
-      <c r="A117" s="14" t="inlineStr"/>
-      <c r="B117" s="15" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr"/>
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C117" s="16" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D117" s="16" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E117" s="14" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>84.0, 66.6</t>
         </is>
       </c>
-      <c r="F117" s="16" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G117" s="17" t="inlineStr">
-        <is>
-          <t>3 脚不对称，贴不反</t>
-        </is>
-      </c>
+      <c r="G117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="19" customHeight="1"/>
     <row r="119" ht="19" customHeight="1">
@@ -4492,7 +4476,7 @@
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>认 pin1（4 脚晶振）</t>
+          <t>认 pin1（4 脚，pin2/4 接地）</t>
         </is>
       </c>
     </row>
@@ -4525,42 +4509,38 @@
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>认 pin1（4 脚晶振）</t>
+          <t>认 pin1（4 脚，pin2/4 接地）</t>
         </is>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
-      <c r="A142" s="14" t="inlineStr"/>
-      <c r="B142" s="15" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr"/>
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="C142" s="16" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>32.768kHz FC-135</t>
         </is>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
         </is>
       </c>
-      <c r="E142" s="14" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>122.7, 91.3</t>
         </is>
       </c>
-      <c r="F142" s="16" t="inlineStr">
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G142" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（4 脚晶振）</t>
-        </is>
-      </c>
+      <c r="G142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="19" customHeight="1"/>
     <row r="144" ht="19" customHeight="1">

--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -4448,68 +4448,68 @@
     </row>
     <row r="139" ht="19" customHeight="1"/>
     <row r="140" ht="19" customHeight="1">
-      <c r="A140" s="14" t="inlineStr"/>
-      <c r="B140" s="15" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr"/>
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C140" s="16" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>12MHz</t>
         </is>
       </c>
-      <c r="D140" s="16" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
-      <c r="E140" s="14" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>100.4, 87.7</t>
         </is>
       </c>
-      <c r="F140" s="16" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G140" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（4 脚，pin2/4 接地）</t>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>无源晶体，转 180° 等价，长边对长边即可</t>
         </is>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
-      <c r="A141" s="14" t="inlineStr"/>
-      <c r="B141" s="15" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr"/>
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="C141" s="16" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>48MHz ABM8W-7pF</t>
         </is>
       </c>
-      <c r="D141" s="16" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
-      <c r="E141" s="14" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>133.8, 81.7</t>
         </is>
       </c>
-      <c r="F141" s="16" t="inlineStr">
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G141" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（4 脚，pin2/4 接地）</t>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>无源晶体，转 180° 等价，长边对长边即可</t>
         </is>
       </c>
     </row>

--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V3.4 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="V3.7 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.4 核对清单'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.7 核对清单'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>55.6, 79.9</t>
+          <t>55.6, 80.1</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>55.6, 84.5</t>
+          <t>55.6, 85.2</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>110.9, 62.1</t>
+          <t>110.2, 61.2</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>76.2, 55.1</t>
+          <t>63.4, 63.3</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>78.9, 55.1</t>
+          <t>56.5, 64.6</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>81.5, 55.1</t>
+          <t>56.3, 62.4</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>95.4, 66.6</t>
+          <t>58.8, 76.4</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>83.6, 71.2</t>
+          <t>61.8, 73.3</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>55.6, 82.3</t>
+          <t>55.6, 82.6</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>92.1, 62.1</t>
+          <t>61.8, 64.8</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>92.1, 66.6</t>
+          <t>58.0, 67.6</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>88.5, 62.1</t>
+          <t>61.8, 67.4</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>88.6, 66.6</t>
+          <t>56.4, 69.7</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>84.0, 62.1</t>
+          <t>61.8, 70.2</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>84.0, 66.6</t>
+          <t>57.8, 72.6</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>73.0, 55.1</t>
+          <t>58.8, 63.3</t>
         </is>
       </c>
       <c r="F135" s="16" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>68.0, 54.5</t>
+          <t>52.9, 74.1</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -4692,244 +4692,244 @@
       <c r="A149" s="2" t="inlineStr"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_IFA_TEST(π后调试口)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>103.1, 61.3</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="2" t="inlineStr"/>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
           <t>J8</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>U.FL→内置patch</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>60.0, 54.5</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>52.9, 64.4</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="19" customHeight="1"/>
-    <row r="151" ht="19" customHeight="1">
-      <c r="A151" s="10" t="inlineStr"/>
-      <c r="B151" s="11" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="19" customHeight="1"/>
+    <row r="152" ht="19" customHeight="1">
+      <c r="A152" s="10" t="inlineStr"/>
+      <c r="B152" s="11" t="inlineStr">
         <is>
           <t>ANT1</t>
         </is>
       </c>
-      <c r="C151" s="12" t="inlineStr">
+      <c r="C152" s="12" t="inlineStr">
         <is>
           <t>IFA_1090</t>
         </is>
       </c>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
         <is>
           <t>ANT_IFA_1090MHz</t>
         </is>
       </c>
-      <c r="E151" s="10" t="inlineStr">
-        <is>
-          <t>102.0, 57.8</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="inlineStr">
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>85.5, 57.8</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
         <is>
           <t>不贴（板载天线）</t>
         </is>
       </c>
-      <c r="G151" s="13" t="inlineStr"/>
-    </row>
-    <row r="152" ht="19" customHeight="1"/>
-    <row r="153" ht="19" customHeight="1">
-      <c r="A153" s="10" t="inlineStr"/>
-      <c r="B153" s="11" t="inlineStr">
-        <is>
-          <t>ZP1</t>
-        </is>
-      </c>
-      <c r="C153" s="12" t="inlineStr">
-        <is>
-          <t>DNP 并-天线侧</t>
-        </is>
-      </c>
-      <c r="D153" s="12" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E153" s="10" t="inlineStr">
-        <is>
-          <t>105.3, 58.2</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G153" s="13" t="inlineStr"/>
-    </row>
+      <c r="G152" s="13" t="inlineStr"/>
+    </row>
+    <row r="153" ht="19" customHeight="1"/>
     <row r="154" ht="19" customHeight="1">
       <c r="A154" s="10" t="inlineStr"/>
       <c r="B154" s="11" t="inlineStr">
         <is>
+          <t>ZP1</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>DNP 并-天线侧</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>85.5, 63.6</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G154" s="13" t="inlineStr"/>
+    </row>
+    <row r="155" ht="19" customHeight="1">
+      <c r="A155" s="10" t="inlineStr"/>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
           <t>ZP2</t>
         </is>
       </c>
-      <c r="C154" s="12" t="inlineStr">
+      <c r="C155" s="12" t="inlineStr">
         <is>
           <t>DNP 并-电台侧</t>
         </is>
       </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t>108.1, 62.1</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="inlineStr">
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>90.5, 63.6</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G154" s="13" t="inlineStr"/>
-    </row>
-    <row r="155" ht="19" customHeight="1"/>
-    <row r="156" ht="19" customHeight="1">
-      <c r="A156" s="2" t="inlineStr"/>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="G155" s="13" t="inlineStr"/>
+    </row>
+    <row r="156" ht="19" customHeight="1"/>
+    <row r="157" ht="19" customHeight="1">
+      <c r="A157" s="2" t="inlineStr"/>
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>ZS1</t>
         </is>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>0R 串</t>
         </is>
       </c>
-      <c r="D156" s="4" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>L_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>104.3, 62.1</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>88.0, 62.9</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G156" s="5" t="inlineStr"/>
-    </row>
-    <row r="157" ht="19" customHeight="1"/>
-    <row r="158" ht="19" customHeight="1">
-      <c r="A158" s="10" t="inlineStr"/>
-      <c r="B158" s="11" t="inlineStr">
-        <is>
-          <t>SW1</t>
-        </is>
-      </c>
-      <c r="C158" s="12" t="inlineStr">
-        <is>
-          <t>RESET短接焊盘</t>
-        </is>
-      </c>
-      <c r="D158" s="12" t="inlineStr">
-        <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
-        </is>
-      </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>88.7, 91.3</t>
-        </is>
-      </c>
-      <c r="F158" s="12" t="inlineStr">
-        <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G158" s="13" t="inlineStr"/>
-    </row>
+      <c r="G157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158" ht="19" customHeight="1"/>
     <row r="159" ht="19" customHeight="1">
       <c r="A159" s="10" t="inlineStr"/>
       <c r="B159" s="11" t="inlineStr">
         <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>RESET短接焊盘</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>88.7, 91.3</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>不贴（短接焊盘）</t>
+        </is>
+      </c>
+      <c r="G159" s="13" t="inlineStr"/>
+    </row>
+    <row r="160" ht="19" customHeight="1">
+      <c r="A160" s="10" t="inlineStr"/>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
           <t>SW2</t>
         </is>
       </c>
-      <c r="C159" s="12" t="inlineStr">
+      <c r="C160" s="12" t="inlineStr">
         <is>
           <t>BOOTSEL短接焊盘</t>
         </is>
       </c>
-      <c r="D159" s="12" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
         </is>
       </c>
-      <c r="E159" s="10" t="inlineStr">
+      <c r="E160" s="10" t="inlineStr">
         <is>
           <t>92.9, 91.3</t>
         </is>
       </c>
-      <c r="F159" s="12" t="inlineStr">
+      <c r="F160" s="12" t="inlineStr">
         <is>
           <t>不贴（短接焊盘）</t>
         </is>
       </c>
-      <c r="G159" s="13" t="inlineStr"/>
-    </row>
-    <row r="160" ht="19" customHeight="1"/>
-    <row r="161" ht="19" customHeight="1">
-      <c r="A161" s="10" t="inlineStr"/>
-      <c r="B161" s="11" t="inlineStr">
-        <is>
-          <t>TP1</t>
-        </is>
-      </c>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D161" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E161" s="10" t="inlineStr">
-        <is>
-          <t>102.0, 91.3</t>
-        </is>
-      </c>
-      <c r="F161" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G161" s="13" t="inlineStr"/>
-    </row>
+      <c r="G160" s="13" t="inlineStr"/>
+    </row>
+    <row r="161" ht="19" customHeight="1"/>
     <row r="162" ht="19" customHeight="1">
       <c r="A162" s="10" t="inlineStr"/>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>TP2</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>104.9, 91.3</t>
+          <t>102.0, 91.3</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="A163" s="10" t="inlineStr"/>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>TP3</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>107.8, 91.3</t>
+          <t>104.9, 91.3</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -4987,7 +4987,7 @@
       <c r="A164" s="10" t="inlineStr"/>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>TP4</t>
+          <t>TP3</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>110.7, 91.3</t>
+          <t>107.8, 91.3</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -5016,7 +5016,7 @@
       <c r="A165" s="10" t="inlineStr"/>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>TP5</t>
+          <t>TP4</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>113.5, 91.3</t>
+          <t>110.7, 91.3</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -5045,7 +5045,7 @@
       <c r="A166" s="10" t="inlineStr"/>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>TP6</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>116.4, 91.3</t>
+          <t>113.5, 91.3</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -5074,66 +5074,66 @@
       <c r="A167" s="10" t="inlineStr"/>
       <c r="B167" s="11" t="inlineStr">
         <is>
+          <t>TP6</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>116.4, 91.3</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G167" s="13" t="inlineStr"/>
+    </row>
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="10" t="inlineStr"/>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
           <t>TP7</t>
         </is>
       </c>
-      <c r="C167" s="12" t="inlineStr">
+      <c r="C168" s="12" t="inlineStr">
         <is>
           <t>TestPoint</t>
         </is>
       </c>
-      <c r="D167" s="12" t="inlineStr">
+      <c r="D168" s="12" t="inlineStr">
         <is>
           <t>TestPoint_Pad_1.0x1.0mm</t>
         </is>
       </c>
-      <c r="E167" s="10" t="inlineStr">
+      <c r="E168" s="10" t="inlineStr">
         <is>
           <t>83.3, 95.2</t>
         </is>
       </c>
-      <c r="F167" s="12" t="inlineStr">
+      <c r="F168" s="12" t="inlineStr">
         <is>
           <t>不贴（测试点焊盘）</t>
         </is>
       </c>
-      <c r="G167" s="13" t="inlineStr"/>
-    </row>
-    <row r="168" ht="19" customHeight="1"/>
-    <row r="169" ht="19" customHeight="1">
-      <c r="A169" s="10" t="inlineStr"/>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C169" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D169" s="12" t="inlineStr">
-        <is>
-          <t>MountingHole_2.7mm_M2.5</t>
-        </is>
-      </c>
-      <c r="E169" s="10" t="inlineStr">
-        <is>
-          <t>54.0, 56.0</t>
-        </is>
-      </c>
-      <c r="F169" s="12" t="inlineStr">
-        <is>
-          <t>不贴（安装孔）</t>
-        </is>
-      </c>
-      <c r="G169" s="13" t="inlineStr"/>
-    </row>
+      <c r="G168" s="13" t="inlineStr"/>
+    </row>
+    <row r="169" ht="19" customHeight="1"/>
     <row r="170" ht="19" customHeight="1">
       <c r="A170" s="10" t="inlineStr"/>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>146.0, 56.0</t>
+          <t>54.0, 56.0</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -5162,7 +5162,7 @@
       <c r="A171" s="10" t="inlineStr"/>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>54.0, 106.0</t>
+          <t>146.0, 56.0</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -5191,30 +5191,59 @@
       <c r="A172" s="10" t="inlineStr"/>
       <c r="B172" s="11" t="inlineStr">
         <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E172" s="10" t="inlineStr">
+        <is>
+          <t>54.0, 106.0</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G172" s="13" t="inlineStr"/>
+    </row>
+    <row r="173" ht="19" customHeight="1">
+      <c r="A173" s="10" t="inlineStr"/>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C172" s="12" t="inlineStr">
+      <c r="C173" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D172" s="12" t="inlineStr">
+      <c r="D173" s="12" t="inlineStr">
         <is>
           <t>MountingHole_2.7mm_M2.5</t>
         </is>
       </c>
-      <c r="E172" s="10" t="inlineStr">
+      <c r="E173" s="10" t="inlineStr">
         <is>
           <t>146.0, 106.0</t>
         </is>
       </c>
-      <c r="F172" s="12" t="inlineStr">
+      <c r="F173" s="12" t="inlineStr">
         <is>
           <t>不贴（安装孔）</t>
         </is>
       </c>
-      <c r="G172" s="13" t="inlineStr"/>
+      <c r="G173" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions gridLines="0"/>

--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V3.7 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="V3.9 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.7 核对清单'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.9 核对清单'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>15pF</t>
+          <t>15pF C0G</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>15pF</t>
+          <t>15pF C0G</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1058,27 +1058,27 @@
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95.7, 95.2</t>
+          <t>101.0, 67.5</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99.8, 95.2</t>
+          <t>95.7, 95.2</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1116,98 +1116,98 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>99.8, 95.2</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>100nF</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>103.8, 95.2</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>100nF</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>109.2, 77.4</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>板上印着 `R33`，尺寸相同会真贴错</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>C26</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>100nF</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>107.8, 95.2</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>111.9, 95.2</t>
+          <t>107.8, 95.2</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1236,12 +1236,12 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86.5, 87.7</t>
+          <t>111.9, 95.2</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1265,103 +1265,103 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>86.5, 87.7</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>1uF</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>89.5, 87.7</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>100pF</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>C_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>120.4, 62.1</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>板上印着 `L14`，尺寸相同会真贴错</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>C31</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>12pF</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>C_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>106.0, 71.2</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>100pF C0G</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114.5, 71.2</t>
+          <t>106.0, 71.2</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1385,12 +1385,12 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>100pF C0G</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>120.9, 71.2</t>
+          <t>114.5, 71.2</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1414,12 +1414,12 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3pF</t>
+          <t>100pF C0G</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>129.4, 71.2</t>
+          <t>120.9, 71.2</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1443,12 +1443,12 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>3pF</t>
+          <t>100pF C0G</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141.2, 71.2</t>
+          <t>129.4, 71.2</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1472,12 +1472,12 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>100pF C0G</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>109.6, 85.0</t>
+          <t>141.2, 71.2</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>137.3, 69.2</t>
+          <t>103.0, 66.5</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1530,12 +1530,12 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>100pF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>140.0, 83.6</t>
+          <t>109.6, 85.0</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
@@ -1559,12 +1559,12 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3.6pF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>123.6, 76.3</t>
+          <t>137.3, 69.2</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -1588,12 +1588,12 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2.7pF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>126.9, 76.3</t>
+          <t>140.0, 83.6</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1617,12 +1617,12 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>6.2pF</t>
+          <t>3.6pF</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>130.2, 76.3</t>
+          <t>123.6, 76.3</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1646,12 +1646,12 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3pF</t>
+          <t>2.7pF</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>137.6, 78.3</t>
+          <t>126.9, 76.3</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1675,12 +1675,12 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3.6pF</t>
+          <t>6.2pF</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>121.7, 78.0</t>
+          <t>130.2, 76.3</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1704,165 +1704,165 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
+          <t>C43</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>3pF</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>137.6, 78.3</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>C44</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>3.6pF</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>121.7, 78.0</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
           <t>C45</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>100pF</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>C_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>119.2, 84.3</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>C46</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>3pF</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>118.8, 86.2</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>118.7, 86.2</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>板上印着 `C47`，尺寸相同会真贴错</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="6" t="inlineStr"/>
-      <c r="B43" s="7" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>C47</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>200pF</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>118.7, 88.4</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>板上印着 `C46`，尺寸相同会真贴错</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>C49</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>100nF</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>55.6, 80.1</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>C51</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>1nF</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>55.6, 85.2</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>60.4, 96.2</t>
+          <t>99.6, 65.5</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -1886,22 +1886,22 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>100pF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>110.2, 61.2</t>
+          <t>55.6, 80.1</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -1915,22 +1915,22 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>100pF</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>105.3, 68.1</t>
+          <t>55.6, 85.2</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -1944,22 +1944,22 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>100pF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>90.2, 74.0</t>
+          <t>60.4, 96.2</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -1973,7 +1973,7 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>85.1, 74.0</t>
+          <t>110.2, 61.2</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>63.4, 63.3</t>
+          <t>105.3, 68.1</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>56.5, 64.6</t>
+          <t>90.2, 74.0</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2070,17 +2070,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>56.3, 62.4</t>
+          <t>85.1, 74.0</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
@@ -2089,27 +2089,27 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>136.2, 93.1</t>
+          <t>63.4, 63.3</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2118,27 +2118,27 @@
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>121.2, 97.0</t>
+          <t>56.5, 64.6</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
@@ -2147,27 +2147,27 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>125.1, 97.0</t>
+          <t>56.3, 62.4</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
@@ -2176,22 +2176,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>129.0, 97.0</t>
+          <t>136.2, 93.1</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>132.9, 97.0</t>
+          <t>121.2, 97.0</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2234,7 +2234,7 @@
       <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>136.8, 97.0</t>
+          <t>125.1, 97.0</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2263,22 +2263,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>123.2, 100.5</t>
+          <t>129.0, 97.0</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2292,12 +2292,12 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>126.9, 93.1</t>
+          <t>132.9, 97.0</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2321,12 +2321,12 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>123.1, 93.8</t>
+          <t>136.8, 97.0</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2350,57 +2350,85 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15pF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
+          <t>C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>123.2, 100.5</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>C67</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>127.7, 100.5</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>126.9, 93.1</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64" ht="19" customHeight="1"/>
+      <c r="G64" s="5" t="inlineStr"/>
+    </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>18pF</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>79.0, 87.2</t>
+          <t>123.1, 93.8</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -2409,27 +2437,27 @@
       <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>18pF</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>61.4, 106.1</t>
+          <t>127.7, 100.5</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -2438,27 +2466,27 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>C81</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>470pF C0G</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>61.4, 108.7</t>
+          <t>118.6, 73.5</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -2467,22 +2495,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>C82</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>110.6, 87.7</t>
+          <t>83.0, 84.5</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2496,22 +2524,22 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>C83</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>95.7, 98.3</t>
+          <t>93.6, 79.5</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2525,22 +2553,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>99.8, 98.3</t>
+          <t>93.6, 82.0</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2554,22 +2582,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>C85</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>103.8, 98.3</t>
+          <t>96.0, 79.5</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2583,22 +2611,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>C86</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>107.8, 98.3</t>
+          <t>96.0, 82.0</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -2612,22 +2640,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>C87</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>27R</t>
+          <t>10nF C0G</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>92.5, 87.7</t>
+          <t>97.8, 84.4</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2637,40 +2665,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr"/>
     </row>
-    <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>27R</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>95.6, 87.7</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr"/>
-    </row>
+    <row r="74" ht="19" customHeight="1"/>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>121.4, 105.2</t>
+          <t>79.0, 87.2</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>136.2, 62.1</t>
+          <t>61.4, 106.1</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
@@ -2728,27 +2728,27 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>138.5, 71.2</t>
+          <t>61.4, 108.7</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr"/>
@@ -2757,12 +2757,12 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>18k(1090实调)</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2772,55 +2772,55 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>132.9, 67.3</t>
+          <t>110.6, 87.7</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="19" customHeight="1">
-      <c r="A79" s="10" t="inlineStr"/>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>R21</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>0R DNP(选8313时贴)</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>115.2, 85.0</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G79" s="13" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>95.7, 98.3</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>87.5, 71.2</t>
+          <t>99.8, 98.3</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -2844,12 +2844,12 @@
       <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2859,84 +2859,84 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>91.4, 71.2</t>
+          <t>103.8, 98.3</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="19" customHeight="1">
-      <c r="A82" s="10" t="inlineStr"/>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t>R24</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>0R DNP(旁路外接)</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>112.7, 66.0</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G82" s="13" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>5.1k</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>107.8, 98.3</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="19" customHeight="1">
-      <c r="A83" s="10" t="inlineStr"/>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>R25</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>0R DNP(旁路板载)</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>114.8, 66.0</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G83" s="13" t="inlineStr"/>
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>27R</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>92.5, 87.7</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>58.8, 76.4</t>
+          <t>95.6, 87.7</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -2960,27 +2960,27 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>3.32k</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>61.8, 73.3</t>
+          <t>98.8, 68.0</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -2989,27 +2989,27 @@
       <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>108.0, 66.6</t>
+          <t>121.4, 105.2</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3018,12 +3018,12 @@
       <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>115.0, 87.3</t>
+          <t>136.2, 62.1</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3047,74 +3047,70 @@
       <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>138.5, 71.2</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>0R</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>112.5, 75.2</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>115.2, 85.0</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="6" t="inlineStr"/>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>R33</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>100k</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>108.7, 75.2</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>板上印着 `C25`，尺寸相同会真贴错</t>
-        </is>
-      </c>
+      <c r="G89" s="5" t="inlineStr"/>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3124,7 +3120,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>55.6, 77.5</t>
+          <t>87.5, 71.2</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3138,12 +3134,12 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3153,7 +3149,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>55.6, 82.6</t>
+          <t>91.4, 71.2</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3164,55 +3160,83 @@
       <c r="G91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="19" customHeight="1">
-      <c r="A92" s="2" t="inlineStr"/>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>R36</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>1k</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>61.4, 103.5</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93" ht="19" customHeight="1"/>
+      <c r="A92" s="10" t="inlineStr"/>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>0R DNP(旁路外接)</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>112.7, 66.0</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr"/>
+    </row>
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="10" t="inlineStr"/>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>0R DNP(旁路板载)</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>114.8, 66.0</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr"/>
+    </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>61.8, 64.8</t>
+          <t>58.8, 76.4</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3226,85 +3250,85 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>131.5, 93.1</t>
+          <t>61.8, 73.3</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="19" customHeight="1">
-      <c r="A96" s="2" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>L8</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>100nH</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>L_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>142.6, 87.0</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr"/>
+      <c r="A96" s="10" t="inlineStr"/>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>1k DNP</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>108.0, 66.6</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="inlineStr"/>
     </row>
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="2" t="inlineStr"/>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>124.2, 78.0</t>
+          <t>115.0, 87.3</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr"/>
@@ -3313,85 +3337,89 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>120.8, 76.3</t>
+          <t>112.5, 75.2</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="19" customHeight="1">
-      <c r="A99" s="2" t="inlineStr"/>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>L11</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>6.8nH</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>L_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>134.2, 76.3</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr"/>
+      <c r="A99" s="6" t="inlineStr"/>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>R33</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>108.7, 75.2</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>板上印着 `C25`，尺寸相同会真贴错</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>L12</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>137.6, 76.3</t>
+          <t>55.6, 77.5</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
@@ -3400,219 +3428,259 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>R35</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>119.2, 83.2</t>
+          <t>55.6, 82.6</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="19" customHeight="1">
-      <c r="A102" s="6" t="inlineStr"/>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>100nH</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>L_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>120.4, 63.3</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>板上印着 `C30`，尺寸相同会真贴错</t>
-        </is>
-      </c>
+      <c r="A102" s="10" t="inlineStr"/>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>R36</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>1k DNP</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>61.4, 103.5</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G102" s="13" t="inlineStr"/>
     </row>
     <row r="103" ht="19" customHeight="1">
       <c r="A103" s="2" t="inlineStr"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>58.0, 67.6</t>
+          <t>132.5, 85.0</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>R50</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>94.0, 85.2</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>R51</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>96.0, 85.2</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>R52</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>60.0, 83.0</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104" ht="19" customHeight="1"/>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="14" t="inlineStr"/>
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>B5819W</t>
-        </is>
-      </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>D_SOD-123</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>97.8, 91.3</t>
-        </is>
-      </c>
-      <c r="F105" s="16" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>有极性，认阴极标记带</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="19" customHeight="1">
-      <c r="A106" s="14" t="inlineStr"/>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>ESD 3.3V/0.6pF</t>
-        </is>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>D_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E106" s="14" t="inlineStr">
-        <is>
-          <t>128.3, 62.1</t>
-        </is>
-      </c>
-      <c r="F106" s="16" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="19" customHeight="1">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>R53</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>63.0, 84.4</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="19" customHeight="1">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>R54</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>10R</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>109.6, 82.1</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G106" s="17" t="inlineStr">
-        <is>
-          <t>有极性，认阴极标记带</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="14" t="inlineStr"/>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>ESD 3.3V/0.6pF</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>D_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E107" s="14" t="inlineStr">
-        <is>
-          <t>140.0, 86.9</t>
-        </is>
-      </c>
-      <c r="F107" s="16" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G107" s="17" t="inlineStr">
-        <is>
-          <t>有极性，认阴极标记带</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="19" customHeight="1"/>
+      <c r="G108" s="5" t="inlineStr"/>
+    </row>
     <row r="109" ht="19" customHeight="1">
       <c r="A109" s="2" t="inlineStr"/>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>R55</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Fuse_0805_2012Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>129.8, 105.2</t>
+          <t>59.1, 80.3</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr"/>
@@ -3621,27 +3689,27 @@
       <c r="A110" s="2" t="inlineStr"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>R56</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Fuse_0805_2012Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>140.2, 62.1</t>
+          <t>132.3, 89.7</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr"/>
@@ -3650,86 +3718,86 @@
       <c r="A111" s="2" t="inlineStr"/>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>R57</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>33R</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Fuse_0805_2012Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>61.8, 67.4</t>
+          <t>85.7, 95.3</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
     </row>
-    <row r="112" ht="19" customHeight="1">
-      <c r="A112" s="2" t="inlineStr"/>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>6V/200mA</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>Fuse_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>56.4, 69.7</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr"/>
-    </row>
-    <row r="113" ht="19" customHeight="1"/>
+    <row r="112" ht="19" customHeight="1"/>
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="2" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>18nH 0402CS-18NXGRW</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>105.5, 69.8</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+    </row>
     <row r="114" ht="19" customHeight="1">
       <c r="A114" s="2" t="inlineStr"/>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>125.1, 105.2</t>
+          <t>61.8, 64.8</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr"/>
@@ -3738,27 +3806,27 @@
       <c r="A115" s="2" t="inlineStr"/>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>132.0, 62.1</t>
+          <t>131.5, 93.1</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -3767,27 +3835,27 @@
       <c r="A116" s="2" t="inlineStr"/>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>61.8, 70.2</t>
+          <t>142.6, 87.0</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr"/>
@@ -3796,1454 +3864,1987 @@
       <c r="A117" s="2" t="inlineStr"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>57.8, 72.6</t>
+          <t>124.2, 78.0</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="2" t="inlineStr"/>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>27nH</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>120.8, 76.3</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="19" customHeight="1">
+      <c r="A119" s="2" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>6.8nH</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>134.2, 76.3</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="19" customHeight="1">
+      <c r="A120" s="2" t="inlineStr"/>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>6.8nH</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>137.6, 76.3</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="19" customHeight="1">
+      <c r="A121" s="2" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>7.5nH</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>119.2, 83.2</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="19" customHeight="1">
+      <c r="A122" s="6" t="inlineStr"/>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>100nH</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>120.4, 63.3</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>板上印着 `C30`，尺寸相同会真贴错</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="19" customHeight="1">
+      <c r="A123" s="2" t="inlineStr"/>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>33nH</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>L_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>58.0, 67.6</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr"/>
-    </row>
-    <row r="118" ht="19" customHeight="1"/>
-    <row r="119" ht="19" customHeight="1">
-      <c r="A119" s="14" t="inlineStr"/>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>ME6211C33M5</t>
-        </is>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E119" s="14" t="inlineStr">
-        <is>
-          <t>69.4, 93.3</t>
-        </is>
-      </c>
-      <c r="F119" s="16" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G119" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="19" customHeight="1">
-      <c r="A120" s="14" t="inlineStr"/>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>TPS7A2033PDBVR</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>63.1, 93.3</t>
-        </is>
-      </c>
-      <c r="F120" s="16" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G120" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="19" customHeight="1">
-      <c r="A121" s="14" t="inlineStr"/>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>TPS7A2033PDBVR</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E121" s="14" t="inlineStr">
-        <is>
-          <t>74.3, 93.3</t>
-        </is>
-      </c>
-      <c r="F121" s="16" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G121" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="19" customHeight="1">
-      <c r="A122" s="14" t="inlineStr"/>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>BNO085</t>
-        </is>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>BNO085_LGA-28</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>63.7, 78.3</t>
-        </is>
-      </c>
-      <c r="F122" s="16" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G122" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="19" customHeight="1">
-      <c r="A123" s="14" t="inlineStr"/>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>BMP388</t>
-        </is>
-      </c>
-      <c r="D123" s="16" t="inlineStr">
-        <is>
-          <t>BMP388_LGA-10</t>
-        </is>
-      </c>
-      <c r="E123" s="14" t="inlineStr">
-        <is>
-          <t>71.3, 81.2</t>
-        </is>
-      </c>
-      <c r="F123" s="16" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G123" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="19" customHeight="1">
-      <c r="A124" s="14" t="inlineStr"/>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>QMC5883P</t>
-        </is>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>LGA-16_3x3mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr">
-        <is>
-          <t>71.3, 77.0</t>
-        </is>
-      </c>
-      <c r="F124" s="16" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
+      <c r="G123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="19" customHeight="1"/>
     <row r="125" ht="19" customHeight="1">
       <c r="A125" s="14" t="inlineStr"/>
       <c r="B125" s="15" t="inlineStr">
         <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>B5819W</t>
+        </is>
+      </c>
+      <c r="D125" s="16" t="inlineStr">
+        <is>
+          <t>D_SOD-123</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>97.8, 91.3</t>
+        </is>
+      </c>
+      <c r="F125" s="16" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>有极性，认阴极标记带</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="19" customHeight="1">
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>128.3, 62.1</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="19" customHeight="1">
+      <c r="A127" s="2" t="inlineStr"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>140.0, 86.9</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="19" customHeight="1">
+      <c r="A128" s="2" t="inlineStr"/>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>60.0, 90.4</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="19" customHeight="1">
+      <c r="A129" s="2" t="inlineStr"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>60.0, 93.6</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="19" customHeight="1"/>
+    <row r="131" ht="19" customHeight="1">
+      <c r="A131" s="2" t="inlineStr"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>129.8, 105.2</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="2" t="inlineStr"/>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>140.2, 62.1</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="19" customHeight="1">
+      <c r="A133" s="2" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>61.8, 67.4</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="2" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>56.4, 69.7</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="19" customHeight="1"/>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="2" t="inlineStr"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>125.1, 105.2</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="19" customHeight="1">
+      <c r="A137" s="2" t="inlineStr"/>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>132.0, 62.1</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="19" customHeight="1">
+      <c r="A138" s="2" t="inlineStr"/>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>61.8, 70.2</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="19" customHeight="1">
+      <c r="A139" s="2" t="inlineStr"/>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>57.8, 72.6</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140" ht="19" customHeight="1"/>
+    <row r="141" ht="19" customHeight="1">
+      <c r="A141" s="14" t="inlineStr"/>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>ME6211C33M5</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>69.4, 93.3</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G141" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="14" t="inlineStr"/>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="C142" s="16" t="inlineStr">
+        <is>
+          <t>TPS7A2033PDBVR</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>63.1, 93.3</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="14" t="inlineStr"/>
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>TPS7A2033PDBVR</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>74.3, 93.3</t>
+        </is>
+      </c>
+      <c r="F143" s="16" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G143" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="19" customHeight="1">
+      <c r="A144" s="14" t="inlineStr"/>
+      <c r="B144" s="15" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>BNO085</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>BNO085_LGA-28</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>63.7, 78.3</t>
+        </is>
+      </c>
+      <c r="F144" s="16" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19" customHeight="1">
+      <c r="A145" s="14" t="inlineStr"/>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="C145" s="16" t="inlineStr">
+        <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>BMP388_LGA-10</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>71.3, 81.2</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G145" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="19" customHeight="1">
+      <c r="A146" s="14" t="inlineStr"/>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>QMC5883P</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>LGA-16_3x3mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>71.3, 77.0</t>
+        </is>
+      </c>
+      <c r="F146" s="16" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G146" s="17" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="19" customHeight="1">
+      <c r="A147" s="14" t="inlineStr"/>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
           <t>U7</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
+      <c r="C147" s="16" t="inlineStr">
         <is>
           <t>ATGM336H-6N-74</t>
         </is>
       </c>
-      <c r="D125" s="16" t="inlineStr">
+      <c r="D147" s="16" t="inlineStr">
         <is>
           <t>ATGM336H_LCC-18</t>
         </is>
       </c>
-      <c r="E125" s="14" t="inlineStr">
+      <c r="E147" s="14" t="inlineStr">
         <is>
           <t>70.4, 66.4</t>
         </is>
       </c>
-      <c r="F125" s="16" t="inlineStr">
+      <c r="F147" s="16" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G125" s="17" t="inlineStr">
+      <c r="G147" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="19" customHeight="1">
-      <c r="A126" s="14" t="inlineStr"/>
-      <c r="B126" s="15" t="inlineStr">
+    <row r="148" ht="19" customHeight="1">
+      <c r="A148" s="14" t="inlineStr"/>
+      <c r="B148" s="15" t="inlineStr">
         <is>
           <t>U8</t>
         </is>
       </c>
-      <c r="C126" s="16" t="inlineStr">
+      <c r="C148" s="16" t="inlineStr">
         <is>
           <t>RP2040</t>
         </is>
       </c>
-      <c r="D126" s="16" t="inlineStr">
+      <c r="D148" s="16" t="inlineStr">
         <is>
           <t>QFN-56-1EP_7x7mm_P0.4mm_EP3.2x3.2mm</t>
         </is>
       </c>
-      <c r="E126" s="14" t="inlineStr">
+      <c r="E148" s="14" t="inlineStr">
         <is>
           <t>88.4, 80.5</t>
         </is>
       </c>
-      <c r="F126" s="16" t="inlineStr">
+      <c r="F148" s="16" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G126" s="17" t="inlineStr">
+      <c r="G148" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="19" customHeight="1">
-      <c r="A127" s="14" t="inlineStr"/>
-      <c r="B127" s="15" t="inlineStr">
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="14" t="inlineStr"/>
+      <c r="B149" s="15" t="inlineStr">
         <is>
           <t>U9</t>
         </is>
       </c>
-      <c r="C127" s="16" t="inlineStr">
+      <c r="C149" s="16" t="inlineStr">
         <is>
           <t>W25Q128JVSIQ</t>
         </is>
       </c>
-      <c r="D127" s="16" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>SOIC-8_5.3x5.3mm_P1.27mm</t>
         </is>
       </c>
-      <c r="E127" s="14" t="inlineStr">
+      <c r="E149" s="14" t="inlineStr">
         <is>
           <t>103.4, 82.1</t>
         </is>
       </c>
-      <c r="F127" s="16" t="inlineStr">
+      <c r="F149" s="16" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G127" s="17" t="inlineStr">
+      <c r="G149" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="14" t="inlineStr"/>
-      <c r="B128" s="15" t="inlineStr">
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="14" t="inlineStr"/>
+      <c r="B150" s="15" t="inlineStr">
         <is>
           <t>U10</t>
         </is>
       </c>
-      <c r="C128" s="16" t="inlineStr">
+      <c r="C150" s="16" t="inlineStr">
         <is>
           <t>CC1312R1F3RGZR</t>
         </is>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>QFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
         </is>
       </c>
-      <c r="E128" s="14" t="inlineStr">
+      <c r="E150" s="14" t="inlineStr">
         <is>
           <t>126.2, 85.0</t>
         </is>
       </c>
-      <c r="F128" s="16" t="inlineStr">
+      <c r="F150" s="16" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G128" s="17" t="inlineStr">
+      <c r="G150" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="19" customHeight="1">
-      <c r="A129" s="14" t="inlineStr"/>
-      <c r="B129" s="15" t="inlineStr">
+    <row r="151" ht="19" customHeight="1">
+      <c r="A151" s="14" t="inlineStr"/>
+      <c r="B151" s="15" t="inlineStr">
         <is>
           <t>U11</t>
         </is>
       </c>
-      <c r="C129" s="16" t="inlineStr">
+      <c r="C151" s="16" t="inlineStr">
         <is>
           <t>QPL9547TR7</t>
         </is>
       </c>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="D151" s="16" t="inlineStr">
         <is>
           <t>DFN-8-1EP_2x2mm_P0.5mm_EP0.86x1.55mm</t>
         </is>
       </c>
-      <c r="E129" s="14" t="inlineStr">
+      <c r="E151" s="14" t="inlineStr">
         <is>
           <t>101.6, 71.2</t>
         </is>
       </c>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="F151" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G129" s="17" t="inlineStr">
+      <c r="G151" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="19" customHeight="1">
-      <c r="A130" s="14" t="inlineStr"/>
-      <c r="B130" s="15" t="inlineStr">
+    <row r="152" ht="19" customHeight="1">
+      <c r="A152" s="14" t="inlineStr"/>
+      <c r="B152" s="15" t="inlineStr">
         <is>
           <t>U12</t>
         </is>
       </c>
-      <c r="C130" s="16" t="inlineStr">
+      <c r="C152" s="16" t="inlineStr">
         <is>
           <t>BGA2817</t>
         </is>
       </c>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
         <is>
           <t>SOT-363_SC-70-6</t>
         </is>
       </c>
-      <c r="E130" s="14" t="inlineStr">
+      <c r="E152" s="14" t="inlineStr">
         <is>
           <t>117.7, 71.2</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
+      <c r="F152" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G130" s="17" t="inlineStr">
+      <c r="G152" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="19" customHeight="1">
-      <c r="A131" s="14" t="inlineStr"/>
-      <c r="B131" s="15" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>AD8319ACPZ-R7(主)</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>AD8319_LFCSP-8-EP</t>
-        </is>
-      </c>
-      <c r="E131" s="14" t="inlineStr">
-        <is>
-          <t>133.9, 71.2</t>
-        </is>
-      </c>
-      <c r="F131" s="16" t="inlineStr">
+    <row r="153" ht="19" customHeight="1">
+      <c r="A153" s="10" t="inlineStr"/>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>AD8313ARMZ</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>MSOP-8_3x3mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>114.1, 82.1</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G131" s="17" t="inlineStr">
+      <c r="G153" s="13" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="19" customHeight="1">
-      <c r="A132" s="10" t="inlineStr"/>
-      <c r="B132" s="11" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>AD8313ARMZ(备,二选一)</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>MSOP-8_3x3mm_P0.65mm</t>
-        </is>
-      </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>114.1, 82.1</t>
-        </is>
-      </c>
-      <c r="F132" s="12" t="inlineStr">
-        <is>
-          <t>不贴（备用检波位（默认贴 U13））</t>
-        </is>
-      </c>
-      <c r="G132" s="13" t="inlineStr"/>
-    </row>
-    <row r="133" ht="19" customHeight="1">
-      <c r="A133" s="14" t="inlineStr"/>
-      <c r="B133" s="15" t="inlineStr">
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="14" t="inlineStr"/>
+      <c r="B154" s="15" t="inlineStr">
         <is>
           <t>U15</t>
         </is>
       </c>
-      <c r="C133" s="16" t="inlineStr">
+      <c r="C154" s="16" t="inlineStr">
         <is>
           <t>TLV3501(TOKMAS)</t>
         </is>
       </c>
-      <c r="D133" s="16" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>SOT-23-6</t>
         </is>
       </c>
-      <c r="E133" s="14" t="inlineStr">
+      <c r="E154" s="14" t="inlineStr">
         <is>
           <t>83.1, 91.3</t>
         </is>
       </c>
-      <c r="F133" s="16" t="inlineStr">
+      <c r="F154" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G133" s="17" t="inlineStr">
+      <c r="G154" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="14" t="inlineStr"/>
-      <c r="B134" s="15" t="inlineStr">
+    <row r="155" ht="19" customHeight="1">
+      <c r="A155" s="14" t="inlineStr"/>
+      <c r="B155" s="15" t="inlineStr">
         <is>
           <t>U16</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr">
-        <is>
-          <t>XA17-G4K(或AS179-92LF)</t>
-        </is>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
         <is>
           <t>SOT-363_SC-70-6</t>
         </is>
       </c>
-      <c r="E134" s="14" t="inlineStr">
+      <c r="E155" s="14" t="inlineStr">
         <is>
           <t>114.6, 62.1</t>
         </is>
       </c>
-      <c r="F134" s="16" t="inlineStr">
+      <c r="F155" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G134" s="17" t="inlineStr">
+      <c r="G155" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="19" customHeight="1">
-      <c r="A135" s="14" t="inlineStr"/>
-      <c r="B135" s="15" t="inlineStr">
+    <row r="156" ht="19" customHeight="1">
+      <c r="A156" s="14" t="inlineStr"/>
+      <c r="B156" s="15" t="inlineStr">
         <is>
           <t>U17</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr">
-        <is>
-          <t>XA17-G4K(或AS179-92LF)</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>SOT-363_SC-70-6</t>
         </is>
       </c>
-      <c r="E135" s="14" t="inlineStr">
+      <c r="E156" s="14" t="inlineStr">
         <is>
           <t>58.8, 63.3</t>
         </is>
       </c>
-      <c r="F135" s="16" t="inlineStr">
+      <c r="F156" s="16" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G135" s="17" t="inlineStr">
+      <c r="G156" s="17" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="19" customHeight="1"/>
-    <row r="137" ht="19" customHeight="1">
-      <c r="A137" s="14" t="inlineStr"/>
-      <c r="B137" s="15" t="inlineStr">
+    <row r="157" ht="19" customHeight="1"/>
+    <row r="158" ht="19" customHeight="1">
+      <c r="A158" s="14" t="inlineStr"/>
+      <c r="B158" s="15" t="inlineStr">
         <is>
           <t>FL1</t>
         </is>
       </c>
-      <c r="C137" s="16" t="inlineStr">
+      <c r="C158" s="16" t="inlineStr">
         <is>
           <t>TA0970A</t>
         </is>
       </c>
-      <c r="D137" s="16" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>TA0970A_SMD3838-6</t>
         </is>
       </c>
-      <c r="E137" s="14" t="inlineStr">
+      <c r="E158" s="14" t="inlineStr">
         <is>
           <t>110.2, 71.2</t>
         </is>
       </c>
-      <c r="F137" s="16" t="inlineStr">
+      <c r="F158" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G137" s="17" t="inlineStr">
+      <c r="G158" s="17" t="inlineStr">
         <is>
           <t>SAW 滤波器分输入输出，贴反不工作</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="19" customHeight="1">
-      <c r="A138" s="14" t="inlineStr"/>
-      <c r="B138" s="15" t="inlineStr">
+    <row r="159" ht="19" customHeight="1">
+      <c r="A159" s="14" t="inlineStr"/>
+      <c r="B159" s="15" t="inlineStr">
         <is>
           <t>FL2</t>
         </is>
       </c>
-      <c r="C138" s="16" t="inlineStr">
+      <c r="C159" s="16" t="inlineStr">
         <is>
           <t>TA0970A</t>
         </is>
       </c>
-      <c r="D138" s="16" t="inlineStr">
+      <c r="D159" s="16" t="inlineStr">
         <is>
           <t>TA0970A_SMD3838-6</t>
         </is>
       </c>
-      <c r="E138" s="14" t="inlineStr">
+      <c r="E159" s="14" t="inlineStr">
         <is>
           <t>125.1, 71.2</t>
         </is>
       </c>
-      <c r="F138" s="16" t="inlineStr">
+      <c r="F159" s="16" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G138" s="17" t="inlineStr">
+      <c r="G159" s="17" t="inlineStr">
         <is>
           <t>SAW 滤波器分输入输出，贴反不工作</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="19" customHeight="1"/>
-    <row r="140" ht="19" customHeight="1">
-      <c r="A140" s="2" t="inlineStr"/>
-      <c r="B140" s="3" t="inlineStr">
+    <row r="160" ht="19" customHeight="1"/>
+    <row r="161" ht="19" customHeight="1">
+      <c r="A161" s="2" t="inlineStr"/>
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>12MHz</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>12MHz CL=10pF ABM8-272-T3</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>100.4, 87.7</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="F161" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="G161" s="5" t="inlineStr">
         <is>
           <t>无源晶体，转 180° 等价，长边对长边即可</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="19" customHeight="1">
-      <c r="A141" s="2" t="inlineStr"/>
-      <c r="B141" s="3" t="inlineStr">
+    <row r="162" ht="19" customHeight="1">
+      <c r="A162" s="2" t="inlineStr"/>
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>48MHz ABM8W-7pF</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>133.8, 81.7</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>无源晶体，转 180° 等价，长边对长边即可</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="19" customHeight="1">
-      <c r="A142" s="2" t="inlineStr"/>
-      <c r="B142" s="3" t="inlineStr">
+    <row r="163" ht="19" customHeight="1">
+      <c r="A163" s="2" t="inlineStr"/>
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>32.768kHz FC-135</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>122.7, 91.3</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143" ht="19" customHeight="1"/>
-    <row r="144" ht="19" customHeight="1">
-      <c r="A144" s="2" t="inlineStr"/>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="G163" s="5" t="inlineStr"/>
+    </row>
+    <row r="164" ht="19" customHeight="1"/>
+    <row r="165" ht="19" customHeight="1">
+      <c r="A165" s="2" t="inlineStr"/>
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>J1</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>J3_HAT_2x20_SMD排针</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>PinHeader_2x20_P2.54mm_Vertical_SMD</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>92.6, 106.3</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>F 对外接口</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr"/>
-    </row>
-    <row r="145" ht="19" customHeight="1">
-      <c r="A145" s="2" t="inlineStr"/>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="G165" s="5" t="inlineStr"/>
+    </row>
+    <row r="166" ht="19" customHeight="1">
+      <c r="A166" s="2" t="inlineStr"/>
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>J2</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>U.FL_GNSS_EXT(经尾线转SMA)</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>52.9, 74.1</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146" ht="19" customHeight="1">
-      <c r="A146" s="2" t="inlineStr"/>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="G166" s="5" t="inlineStr"/>
+    </row>
+    <row r="167" ht="19" customHeight="1">
+      <c r="A167" s="2" t="inlineStr"/>
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>J4</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>USB-C_16P</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>USB_C_Receptacle_HRO_TYPE-C-31-M-12</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>53.5, 92.0</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147" ht="19" customHeight="1">
-      <c r="A147" s="2" t="inlineStr"/>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="G167" s="5" t="inlineStr"/>
+    </row>
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="2" t="inlineStr"/>
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>J5</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>U.FL_978</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>145.5, 83.5</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr"/>
-    </row>
-    <row r="148" ht="19" customHeight="1">
-      <c r="A148" s="2" t="inlineStr"/>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr"/>
+    </row>
+    <row r="169" ht="19" customHeight="1">
+      <c r="A169" s="2" t="inlineStr"/>
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>J6</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>U.FL_1090_EXT(经尾线转SMA)</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>124.3, 62.1</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G148" s="5" t="inlineStr"/>
-    </row>
-    <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="2" t="inlineStr"/>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="G169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170" ht="19" customHeight="1">
+      <c r="A170" s="2" t="inlineStr"/>
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>J7</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>U.FL_IFA_TEST(π后调试口)</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>103.1, 61.3</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="19" customHeight="1">
-      <c r="A150" s="2" t="inlineStr"/>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="G170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171" ht="19" customHeight="1">
+      <c r="A171" s="2" t="inlineStr"/>
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>J8</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
         <is>
           <t>U.FL→内置patch</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D171" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>52.9, 64.4</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr"/>
-    </row>
-    <row r="151" ht="19" customHeight="1"/>
-    <row r="152" ht="19" customHeight="1">
-      <c r="A152" s="10" t="inlineStr"/>
-      <c r="B152" s="11" t="inlineStr">
-        <is>
-          <t>ANT1</t>
-        </is>
-      </c>
-      <c r="C152" s="12" t="inlineStr">
-        <is>
-          <t>IFA_1090</t>
-        </is>
-      </c>
-      <c r="D152" s="12" t="inlineStr">
-        <is>
-          <t>ANT_IFA_1090MHz</t>
-        </is>
-      </c>
-      <c r="E152" s="10" t="inlineStr">
-        <is>
-          <t>85.5, 57.8</t>
-        </is>
-      </c>
-      <c r="F152" s="12" t="inlineStr">
-        <is>
-          <t>不贴（板载天线）</t>
-        </is>
-      </c>
-      <c r="G152" s="13" t="inlineStr"/>
-    </row>
-    <row r="153" ht="19" customHeight="1"/>
-    <row r="154" ht="19" customHeight="1">
-      <c r="A154" s="10" t="inlineStr"/>
-      <c r="B154" s="11" t="inlineStr">
-        <is>
-          <t>ZP1</t>
-        </is>
-      </c>
-      <c r="C154" s="12" t="inlineStr">
-        <is>
-          <t>DNP 并-天线侧</t>
-        </is>
-      </c>
-      <c r="D154" s="12" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t>85.5, 63.6</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G154" s="13" t="inlineStr"/>
-    </row>
-    <row r="155" ht="19" customHeight="1">
-      <c r="A155" s="10" t="inlineStr"/>
-      <c r="B155" s="11" t="inlineStr">
-        <is>
-          <t>ZP2</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="inlineStr">
-        <is>
-          <t>DNP 并-电台侧</t>
-        </is>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E155" s="10" t="inlineStr">
-        <is>
-          <t>90.5, 63.6</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G155" s="13" t="inlineStr"/>
-    </row>
-    <row r="156" ht="19" customHeight="1"/>
-    <row r="157" ht="19" customHeight="1">
-      <c r="A157" s="2" t="inlineStr"/>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>ZS1</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>0R 串</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>L_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>88.0, 62.9</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
-    </row>
-    <row r="158" ht="19" customHeight="1"/>
-    <row r="159" ht="19" customHeight="1">
-      <c r="A159" s="10" t="inlineStr"/>
-      <c r="B159" s="11" t="inlineStr">
-        <is>
-          <t>SW1</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="inlineStr">
-        <is>
-          <t>RESET短接焊盘</t>
-        </is>
-      </c>
-      <c r="D159" s="12" t="inlineStr">
-        <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
-        </is>
-      </c>
-      <c r="E159" s="10" t="inlineStr">
-        <is>
-          <t>88.7, 91.3</t>
-        </is>
-      </c>
-      <c r="F159" s="12" t="inlineStr">
-        <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G159" s="13" t="inlineStr"/>
-    </row>
-    <row r="160" ht="19" customHeight="1">
-      <c r="A160" s="10" t="inlineStr"/>
-      <c r="B160" s="11" t="inlineStr">
-        <is>
-          <t>SW2</t>
-        </is>
-      </c>
-      <c r="C160" s="12" t="inlineStr">
-        <is>
-          <t>BOOTSEL短接焊盘</t>
-        </is>
-      </c>
-      <c r="D160" s="12" t="inlineStr">
-        <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
-        </is>
-      </c>
-      <c r="E160" s="10" t="inlineStr">
-        <is>
-          <t>92.9, 91.3</t>
-        </is>
-      </c>
-      <c r="F160" s="12" t="inlineStr">
-        <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G160" s="13" t="inlineStr"/>
-    </row>
-    <row r="161" ht="19" customHeight="1"/>
-    <row r="162" ht="19" customHeight="1">
-      <c r="A162" s="10" t="inlineStr"/>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t>TP1</t>
-        </is>
-      </c>
-      <c r="C162" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D162" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E162" s="10" t="inlineStr">
-        <is>
-          <t>102.0, 91.3</t>
-        </is>
-      </c>
-      <c r="F162" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G162" s="13" t="inlineStr"/>
-    </row>
-    <row r="163" ht="19" customHeight="1">
-      <c r="A163" s="10" t="inlineStr"/>
-      <c r="B163" s="11" t="inlineStr">
-        <is>
-          <t>TP2</t>
-        </is>
-      </c>
-      <c r="C163" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t>104.9, 91.3</t>
-        </is>
-      </c>
-      <c r="F163" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G163" s="13" t="inlineStr"/>
-    </row>
-    <row r="164" ht="19" customHeight="1">
-      <c r="A164" s="10" t="inlineStr"/>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>TP3</t>
-        </is>
-      </c>
-      <c r="C164" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D164" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E164" s="10" t="inlineStr">
-        <is>
-          <t>107.8, 91.3</t>
-        </is>
-      </c>
-      <c r="F164" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G164" s="13" t="inlineStr"/>
-    </row>
-    <row r="165" ht="19" customHeight="1">
-      <c r="A165" s="10" t="inlineStr"/>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>TP4</t>
-        </is>
-      </c>
-      <c r="C165" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D165" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E165" s="10" t="inlineStr">
-        <is>
-          <t>110.7, 91.3</t>
-        </is>
-      </c>
-      <c r="F165" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G165" s="13" t="inlineStr"/>
-    </row>
-    <row r="166" ht="19" customHeight="1">
-      <c r="A166" s="10" t="inlineStr"/>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t>TP5</t>
-        </is>
-      </c>
-      <c r="C166" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D166" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E166" s="10" t="inlineStr">
-        <is>
-          <t>113.5, 91.3</t>
-        </is>
-      </c>
-      <c r="F166" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G166" s="13" t="inlineStr"/>
-    </row>
-    <row r="167" ht="19" customHeight="1">
-      <c r="A167" s="10" t="inlineStr"/>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>TP6</t>
-        </is>
-      </c>
-      <c r="C167" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D167" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E167" s="10" t="inlineStr">
-        <is>
-          <t>116.4, 91.3</t>
-        </is>
-      </c>
-      <c r="F167" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G167" s="13" t="inlineStr"/>
-    </row>
-    <row r="168" ht="19" customHeight="1">
-      <c r="A168" s="10" t="inlineStr"/>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>TP7</t>
-        </is>
-      </c>
-      <c r="C168" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D168" s="12" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E168" s="10" t="inlineStr">
-        <is>
-          <t>83.3, 95.2</t>
-        </is>
-      </c>
-      <c r="F168" s="12" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G168" s="13" t="inlineStr"/>
-    </row>
-    <row r="169" ht="19" customHeight="1"/>
-    <row r="170" ht="19" customHeight="1">
-      <c r="A170" s="10" t="inlineStr"/>
-      <c r="B170" s="11" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C170" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D170" s="12" t="inlineStr">
-        <is>
-          <t>MountingHole_2.7mm_M2.5</t>
-        </is>
-      </c>
-      <c r="E170" s="10" t="inlineStr">
-        <is>
-          <t>54.0, 56.0</t>
-        </is>
-      </c>
-      <c r="F170" s="12" t="inlineStr">
-        <is>
-          <t>不贴（安装孔）</t>
-        </is>
-      </c>
-      <c r="G170" s="13" t="inlineStr"/>
-    </row>
-    <row r="171" ht="19" customHeight="1">
-      <c r="A171" s="10" t="inlineStr"/>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C171" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D171" s="12" t="inlineStr">
-        <is>
-          <t>MountingHole_2.7mm_M2.5</t>
-        </is>
-      </c>
-      <c r="E171" s="10" t="inlineStr">
-        <is>
-          <t>146.0, 56.0</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>不贴（安装孔）</t>
-        </is>
-      </c>
-      <c r="G171" s="13" t="inlineStr"/>
-    </row>
-    <row r="172" ht="19" customHeight="1">
-      <c r="A172" s="10" t="inlineStr"/>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C172" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D172" s="12" t="inlineStr">
-        <is>
-          <t>MountingHole_2.7mm_M2.5</t>
-        </is>
-      </c>
-      <c r="E172" s="10" t="inlineStr">
-        <is>
-          <t>54.0, 106.0</t>
-        </is>
-      </c>
-      <c r="F172" s="12" t="inlineStr">
-        <is>
-          <t>不贴（安装孔）</t>
-        </is>
-      </c>
-      <c r="G172" s="13" t="inlineStr"/>
-    </row>
+      <c r="G171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172" ht="19" customHeight="1"/>
     <row r="173" ht="19" customHeight="1">
       <c r="A173" s="10" t="inlineStr"/>
       <c r="B173" s="11" t="inlineStr">
         <is>
+          <t>ANT1</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>IFA_1090</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>ANT_IFA_1090MHz</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>85.5, 57.8</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>不贴（板载天线）</t>
+        </is>
+      </c>
+      <c r="G173" s="13" t="inlineStr"/>
+    </row>
+    <row r="174" ht="19" customHeight="1"/>
+    <row r="175" ht="19" customHeight="1">
+      <c r="A175" s="10" t="inlineStr"/>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>ZP1</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>DNP 并-天线侧</t>
+        </is>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>85.5, 63.6</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G175" s="13" t="inlineStr"/>
+    </row>
+    <row r="176" ht="19" customHeight="1">
+      <c r="A176" s="10" t="inlineStr"/>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>ZP2</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>DNP 并-电台侧</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="inlineStr">
+        <is>
+          <t>90.5, 63.6</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G176" s="13" t="inlineStr"/>
+    </row>
+    <row r="177" ht="19" customHeight="1"/>
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="2" t="inlineStr"/>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>ZS1</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>0R 串</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>L_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>88.0, 62.9</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr"/>
+    </row>
+    <row r="179" ht="19" customHeight="1"/>
+    <row r="180" ht="19" customHeight="1">
+      <c r="A180" s="10" t="inlineStr"/>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>RESET短接焊盘</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="inlineStr">
+        <is>
+          <t>88.7, 91.3</t>
+        </is>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
+        <is>
+          <t>不贴（短接焊盘）</t>
+        </is>
+      </c>
+      <c r="G180" s="13" t="inlineStr"/>
+    </row>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="10" t="inlineStr"/>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>SW2</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>BOOTSEL短接焊盘</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>92.9, 91.3</t>
+        </is>
+      </c>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>不贴（短接焊盘）</t>
+        </is>
+      </c>
+      <c r="G181" s="13" t="inlineStr"/>
+    </row>
+    <row r="182" ht="19" customHeight="1"/>
+    <row r="183" ht="19" customHeight="1">
+      <c r="A183" s="10" t="inlineStr"/>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>102.0, 91.3</t>
+        </is>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G183" s="13" t="inlineStr"/>
+    </row>
+    <row r="184" ht="19" customHeight="1">
+      <c r="A184" s="10" t="inlineStr"/>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="inlineStr">
+        <is>
+          <t>104.9, 91.3</t>
+        </is>
+      </c>
+      <c r="F184" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G184" s="13" t="inlineStr"/>
+    </row>
+    <row r="185" ht="19" customHeight="1">
+      <c r="A185" s="10" t="inlineStr"/>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>TP3</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D185" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>107.8, 91.3</t>
+        </is>
+      </c>
+      <c r="F185" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G185" s="13" t="inlineStr"/>
+    </row>
+    <row r="186" ht="19" customHeight="1">
+      <c r="A186" s="10" t="inlineStr"/>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>TP4</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>110.7, 91.3</t>
+        </is>
+      </c>
+      <c r="F186" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G186" s="13" t="inlineStr"/>
+    </row>
+    <row r="187" ht="19" customHeight="1">
+      <c r="A187" s="10" t="inlineStr"/>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>TP5</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D187" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>113.5, 91.3</t>
+        </is>
+      </c>
+      <c r="F187" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G187" s="13" t="inlineStr"/>
+    </row>
+    <row r="188" ht="19" customHeight="1">
+      <c r="A188" s="10" t="inlineStr"/>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>TP6</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D188" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E188" s="10" t="inlineStr">
+        <is>
+          <t>116.4, 91.3</t>
+        </is>
+      </c>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G188" s="13" t="inlineStr"/>
+    </row>
+    <row r="189" ht="19" customHeight="1">
+      <c r="A189" s="10" t="inlineStr"/>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>TP7</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D189" s="12" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>80.7, 78.7</t>
+        </is>
+      </c>
+      <c r="F189" s="12" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G189" s="13" t="inlineStr"/>
+    </row>
+    <row r="190" ht="19" customHeight="1"/>
+    <row r="191" ht="19" customHeight="1">
+      <c r="A191" s="10" t="inlineStr"/>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>54.0, 56.0</t>
+        </is>
+      </c>
+      <c r="F191" s="12" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G191" s="13" t="inlineStr"/>
+    </row>
+    <row r="192" ht="19" customHeight="1">
+      <c r="A192" s="10" t="inlineStr"/>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>146.0, 56.0</t>
+        </is>
+      </c>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr"/>
+    </row>
+    <row r="193" ht="19" customHeight="1">
+      <c r="A193" s="10" t="inlineStr"/>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>54.0, 106.0</t>
+        </is>
+      </c>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G193" s="13" t="inlineStr"/>
+    </row>
+    <row r="194" ht="19" customHeight="1">
+      <c r="A194" s="10" t="inlineStr"/>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C173" s="12" t="inlineStr">
+      <c r="C194" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D173" s="12" t="inlineStr">
+      <c r="D194" s="12" t="inlineStr">
         <is>
           <t>MountingHole_2.7mm_M2.5</t>
         </is>
       </c>
-      <c r="E173" s="10" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
         <is>
           <t>146.0, 106.0</t>
         </is>
       </c>
-      <c r="F173" s="12" t="inlineStr">
+      <c r="F194" s="12" t="inlineStr">
         <is>
           <t>不贴（安装孔）</t>
         </is>
       </c>
-      <c r="G173" s="13" t="inlineStr"/>
+      <c r="G194" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions gridLines="0"/>

--- a/hardware/expansion-board-v3/CHECKLIST.xlsx
+++ b/hardware/expansion-board-v3/CHECKLIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V3.9 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3.10 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.9 核对清单'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'V3.10 核对清单'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
